--- a/college-production-tracker.xlsx
+++ b/college-production-tracker.xlsx
@@ -1409,27 +1409,27 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
     </row>

--- a/college-production-tracker.xlsx
+++ b/college-production-tracker.xlsx
@@ -1441,27 +1441,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
     </row>

--- a/college-production-tracker.xlsx
+++ b/college-production-tracker.xlsx
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Created + Audited</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
